--- a/artfynd/A 20880-2023 artfynd.xlsx
+++ b/artfynd/A 20880-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121668083</v>
+        <v>121668081</v>
       </c>
       <c r="B2" t="n">
-        <v>78614</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621131</v>
+        <v>621129</v>
       </c>
       <c r="R2" t="n">
-        <v>6937372</v>
+        <v>6937376</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121668081</v>
+        <v>121668082</v>
       </c>
       <c r="B3" t="n">
-        <v>98110</v>
+        <v>82400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621129</v>
+        <v>621132</v>
       </c>
       <c r="R3" t="n">
-        <v>6937376</v>
+        <v>6937374</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
         <v>121668084</v>
       </c>
       <c r="B4" t="n">
-        <v>78614</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121668082</v>
+        <v>121668083</v>
       </c>
       <c r="B5" t="n">
-        <v>82398</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621132</v>
+        <v>621131</v>
       </c>
       <c r="R5" t="n">
-        <v>6937374</v>
+        <v>6937372</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 20880-2023 artfynd.xlsx
+++ b/artfynd/A 20880-2023 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121668082</v>
+        <v>121668084</v>
       </c>
       <c r="B3" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621132</v>
+        <v>621137</v>
       </c>
       <c r="R3" t="n">
-        <v>6937374</v>
+        <v>6937373</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121668084</v>
+        <v>121668082</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621137</v>
+        <v>621132</v>
       </c>
       <c r="R4" t="n">
-        <v>6937373</v>
+        <v>6937374</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20880-2023 artfynd.xlsx
+++ b/artfynd/A 20880-2023 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121668084</v>
+        <v>121668082</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621137</v>
+        <v>621132</v>
       </c>
       <c r="R3" t="n">
-        <v>6937373</v>
+        <v>6937374</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121668082</v>
+        <v>121668084</v>
       </c>
       <c r="B4" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621132</v>
+        <v>621137</v>
       </c>
       <c r="R4" t="n">
-        <v>6937374</v>
+        <v>6937373</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20880-2023 artfynd.xlsx
+++ b/artfynd/A 20880-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121668083</v>
+        <v>121668084</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621131</v>
+        <v>621137</v>
       </c>
       <c r="R2" t="n">
-        <v>6937372</v>
+        <v>6937373</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121668081</v>
+        <v>121668082</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>82400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621129</v>
+        <v>621132</v>
       </c>
       <c r="R3" t="n">
-        <v>6937376</v>
+        <v>6937374</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121668082</v>
+        <v>121668081</v>
       </c>
       <c r="B4" t="n">
-        <v>82400</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +911,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621132</v>
+        <v>621129</v>
       </c>
       <c r="R4" t="n">
-        <v>6937374</v>
+        <v>6937376</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121668084</v>
+        <v>121668083</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621137</v>
+        <v>621131</v>
       </c>
       <c r="R5" t="n">
-        <v>6937373</v>
+        <v>6937372</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 20880-2023 artfynd.xlsx
+++ b/artfynd/A 20880-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121668082</v>
+        <v>121668083</v>
       </c>
       <c r="B3" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621132</v>
+        <v>621131</v>
       </c>
       <c r="R3" t="n">
-        <v>6937374</v>
+        <v>6937372</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121668083</v>
+        <v>121668082</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621131</v>
+        <v>621132</v>
       </c>
       <c r="R5" t="n">
-        <v>6937372</v>
+        <v>6937374</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 20880-2023 artfynd.xlsx
+++ b/artfynd/A 20880-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121668084</v>
+        <v>121668081</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621137</v>
+        <v>621129</v>
       </c>
       <c r="R2" t="n">
-        <v>6937373</v>
+        <v>6937376</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121668083</v>
+        <v>121668084</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621131</v>
+        <v>621137</v>
       </c>
       <c r="R3" t="n">
-        <v>6937372</v>
+        <v>6937373</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121668081</v>
+        <v>121668083</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +915,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621129</v>
+        <v>621131</v>
       </c>
       <c r="R4" t="n">
-        <v>6937376</v>
+        <v>6937372</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20880-2023 artfynd.xlsx
+++ b/artfynd/A 20880-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121668081</v>
+        <v>121668084</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621129</v>
+        <v>621137</v>
       </c>
       <c r="R2" t="n">
-        <v>6937376</v>
+        <v>6937373</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121668084</v>
+        <v>121668082</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621137</v>
+        <v>621132</v>
       </c>
       <c r="R3" t="n">
-        <v>6937373</v>
+        <v>6937374</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121668083</v>
+        <v>121668081</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +911,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621131</v>
+        <v>621129</v>
       </c>
       <c r="R4" t="n">
-        <v>6937372</v>
+        <v>6937376</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121668082</v>
+        <v>121668083</v>
       </c>
       <c r="B5" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621132</v>
+        <v>621131</v>
       </c>
       <c r="R5" t="n">
-        <v>6937374</v>
+        <v>6937372</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 20880-2023 artfynd.xlsx
+++ b/artfynd/A 20880-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121668084</v>
+        <v>121668082</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621137</v>
+        <v>621132</v>
       </c>
       <c r="R2" t="n">
-        <v>6937373</v>
+        <v>6937374</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121668082</v>
+        <v>121668083</v>
       </c>
       <c r="B3" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621132</v>
+        <v>621131</v>
       </c>
       <c r="R3" t="n">
-        <v>6937374</v>
+        <v>6937372</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121668081</v>
+        <v>121668084</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621129</v>
+        <v>621137</v>
       </c>
       <c r="R4" t="n">
-        <v>6937376</v>
+        <v>6937373</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121668083</v>
+        <v>121668081</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1023,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621131</v>
+        <v>621129</v>
       </c>
       <c r="R5" t="n">
-        <v>6937372</v>
+        <v>6937376</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 20880-2023 artfynd.xlsx
+++ b/artfynd/A 20880-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121668082</v>
+        <v>121668084</v>
       </c>
       <c r="B2" t="n">
-        <v>82400</v>
+        <v>78629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621132</v>
+        <v>621137</v>
       </c>
       <c r="R2" t="n">
-        <v>6937374</v>
+        <v>6937373</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>121668083</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121668084</v>
+        <v>121668082</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>82414</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621137</v>
+        <v>621132</v>
       </c>
       <c r="R4" t="n">
-        <v>6937373</v>
+        <v>6937374</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>121668081</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20880-2023 artfynd.xlsx
+++ b/artfynd/A 20880-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121668084</v>
       </c>
       <c r="B2" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121668083</v>
+        <v>121668082</v>
       </c>
       <c r="B3" t="n">
-        <v>78629</v>
+        <v>82416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621131</v>
+        <v>621132</v>
       </c>
       <c r="R3" t="n">
-        <v>6937372</v>
+        <v>6937374</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121668082</v>
+        <v>121668083</v>
       </c>
       <c r="B4" t="n">
-        <v>82414</v>
+        <v>78631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621132</v>
+        <v>621131</v>
       </c>
       <c r="R4" t="n">
-        <v>6937374</v>
+        <v>6937372</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>121668081</v>
       </c>
       <c r="B5" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20880-2023 artfynd.xlsx
+++ b/artfynd/A 20880-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121668084</v>
+        <v>121668083</v>
       </c>
       <c r="B2" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621137</v>
+        <v>621131</v>
       </c>
       <c r="R2" t="n">
-        <v>6937373</v>
+        <v>6937372</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121668082</v>
+        <v>121668084</v>
       </c>
       <c r="B3" t="n">
-        <v>82416</v>
+        <v>78632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621132</v>
+        <v>621137</v>
       </c>
       <c r="R3" t="n">
-        <v>6937374</v>
+        <v>6937373</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121668083</v>
+        <v>121668081</v>
       </c>
       <c r="B4" t="n">
-        <v>78631</v>
+        <v>98140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621131</v>
+        <v>621129</v>
       </c>
       <c r="R4" t="n">
-        <v>6937372</v>
+        <v>6937376</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121668081</v>
+        <v>121668082</v>
       </c>
       <c r="B5" t="n">
-        <v>98133</v>
+        <v>82417</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,42 +1027,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621129</v>
+        <v>621132</v>
       </c>
       <c r="R5" t="n">
-        <v>6937376</v>
+        <v>6937374</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
